--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRDeviceUseStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
